--- a/Employee_Reports_wi52/Raymond Ian Montero Q0216.xlsx
+++ b/Employee_Reports_wi52/Raymond Ian Montero Q0216.xlsx
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-378</v>
+        <v>-386</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -594,11 +594,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -631,11 +631,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -668,11 +668,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
